--- a/Client/Configs/GameConfig/Datas/enemy.xlsx
+++ b/Client/Configs/GameConfig/Datas/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,35 +459,40 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>baseExp</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>moveSpeed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>attackRange</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>attackInterval</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>aggroRadius</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>movePriority</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>templateKey</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>visualScale</t>
         </is>
@@ -536,35 +541,40 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -573,154 +583,164 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enemy id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Program key.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Display name.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prefab path.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Base hp.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Base attack.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Base defense.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Move speed.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Attack range.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Attack interval.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Aggro radius.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Move priority.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Local template key.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Visual scale.</t>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy id.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Program key.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Display name.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Prefab path.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Base hp.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Base attack.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Base defense.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Base exp reward.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Move speed.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Attack range.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Attack interval.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Aggro radius.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Move priority.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Local template key.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Visual scale.</t>
         </is>
       </c>
     </row>
@@ -748,26 +768,29 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J5" t="n">
         <v>2.4</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>1.6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1.8</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>6</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>70</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -795,26 +818,29 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>42</v>
+      </c>
+      <c r="J6" t="n">
         <v>2.8</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1.7</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1.55</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>80</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Enemy1</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -842,26 +868,29 @@
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>240</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L7" t="n">
         <v>1.65</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>100</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Enemy3</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>3</v>
       </c>
     </row>
